--- a/data/valuations/NFLX/NFLX_modelo_valoracion.xlsx
+++ b/data/valuations/NFLX/NFLX_modelo_valoracion.xlsx
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0.01243346582621872</v>
+        <v>0.01208319811520797</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>0.01243346582621872</v>
+        <v>0.01208319811520797</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>0.01243346582621872</v>
+        <v>0.01208319811520797</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>0.01243346582621872</v>
+        <v>0.01208319811520797</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>0.01243346582621872</v>
+        <v>0.01208319811520797</v>
       </c>
     </row>
     <row r="32">
@@ -1137,7 +1137,7 @@
         </is>
       </c>
       <c r="C35" s="6" t="n">
-        <v>0.1351</v>
+        <v>0.1357</v>
       </c>
     </row>
     <row r="36">
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="C36" s="6" t="n">
-        <v>0.1251</v>
+        <v>0.1257</v>
       </c>
     </row>
     <row r="37">
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>0.1451</v>
+        <v>0.1457</v>
       </c>
     </row>
     <row r="38">
@@ -3285,7 +3285,7 @@
         </is>
       </c>
       <c r="F2" s="16" t="n">
-        <v>91.81999999999999</v>
+        <v>93.43000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -3584,7 +3584,7 @@
         </is>
       </c>
       <c r="K21" s="8">
-        <f>K12*$C$16</f>
+        <f>K8*$C$16</f>
         <v/>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
         </is>
       </c>
       <c r="C34" s="20">
-        <f>C33/91.82-1</f>
+        <f>C33/93.43-1</f>
         <v/>
       </c>
     </row>
@@ -3753,176 +3753,176 @@
     </row>
     <row r="39">
       <c r="A39" s="21" t="n">
-        <v>0.1051</v>
+        <v>0.1057</v>
       </c>
       <c r="C39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$12*11/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*11/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$12*13/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*13/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$12*15/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*15/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$12*17/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*17/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$12*19/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*19/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="21" t="n">
-        <v>0.1151</v>
+        <v>0.1157</v>
       </c>
       <c r="C40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$12*11/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*11/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$12*13/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*13/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$12*15/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*15/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$12*17/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*17/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$12*19/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*19/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="21" t="n">
-        <v>0.1251</v>
+        <v>0.1257</v>
       </c>
       <c r="C41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$12*11/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*11/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$12*13/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*13/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$12*15/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*15/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$12*17/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*17/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$12*19/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*19/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="21" t="n">
-        <v>0.1351</v>
+        <v>0.1357</v>
       </c>
       <c r="C42" s="22">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$12*11/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*11/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D42" s="22">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$12*13/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*13/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E42" s="23">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$12*15/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*15/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F42" s="22">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$12*17/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*17/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G42" s="22">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$12*19/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*19/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="21" t="n">
-        <v>0.1451</v>
+        <v>0.1457</v>
       </c>
       <c r="C43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$12*11/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*11/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$12*13/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*13/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$12*15/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*15/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$12*17/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*17/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$12*19/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*19/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="21" t="n">
-        <v>0.1551</v>
+        <v>0.1557</v>
       </c>
       <c r="C44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$12*11/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*11/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$12*13/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*13/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$12*15/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*15/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$12*17/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*17/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$12*19/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*19/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="21" t="n">
-        <v>0.1651</v>
+        <v>0.1657</v>
       </c>
       <c r="C45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$12*11/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*11/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$12*13/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*13/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$12*15/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*15/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$12*17/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*17/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$12*19/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*19/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>

--- a/data/valuations/NFLX/NFLX_modelo_valoracion.xlsx
+++ b/data/valuations/NFLX/NFLX_modelo_valoracion.xlsx
@@ -868,19 +868,19 @@
         </is>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.01</v>
+        <v>0.06489230588136077</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.01</v>
+        <v>0.06489230588136077</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.01</v>
+        <v>0.06489230588136077</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.01</v>
+        <v>0.06489230588136077</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>0.01</v>
+        <v>0.06489230588136077</v>
       </c>
     </row>
     <row r="21">
@@ -890,19 +890,19 @@
         </is>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.01</v>
+        <v>0.05989230588136077</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.01</v>
+        <v>0.05989230588136077</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.01</v>
+        <v>0.05989230588136077</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.01</v>
+        <v>0.05989230588136077</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>0.01</v>
+        <v>0.05989230588136077</v>
       </c>
     </row>
     <row r="22">
@@ -912,19 +912,19 @@
         </is>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.01</v>
+        <v>0.06989230588136078</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.01</v>
+        <v>0.06989230588136078</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.01</v>
+        <v>0.06989230588136078</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.01</v>
+        <v>0.06989230588136078</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0.01</v>
+        <v>0.06989230588136078</v>
       </c>
     </row>
     <row r="23">
@@ -1137,7 +1137,7 @@
         </is>
       </c>
       <c r="C35" s="6" t="n">
-        <v>0.1357</v>
+        <v>0.1333</v>
       </c>
     </row>
     <row r="36">
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="C36" s="6" t="n">
-        <v>0.1257</v>
+        <v>0.1233</v>
       </c>
     </row>
     <row r="37">
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>0.1457</v>
+        <v>0.1433</v>
       </c>
     </row>
     <row r="38">
@@ -1567,10 +1567,10 @@
         <v>0.995</v>
       </c>
       <c r="D23" s="12" t="n">
-        <v>1.2</v>
+        <v>1.203</v>
       </c>
       <c r="E23" s="12" t="n">
-        <v>1.98</v>
+        <v>1.983</v>
       </c>
       <c r="F23" s="12" t="n">
         <v>2.53</v>
@@ -3285,7 +3285,7 @@
         </is>
       </c>
       <c r="F2" s="16" t="n">
-        <v>93.43000000000001</v>
+        <v>98.66</v>
       </c>
     </row>
     <row r="4">
@@ -3698,7 +3698,7 @@
         </is>
       </c>
       <c r="C34" s="20">
-        <f>C33/93.43-1</f>
+        <f>C33/98.66-1</f>
         <v/>
       </c>
     </row>
@@ -3753,7 +3753,7 @@
     </row>
     <row r="39">
       <c r="A39" s="21" t="n">
-        <v>0.1057</v>
+        <v>0.1033</v>
       </c>
       <c r="C39" s="22">
         <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*11/(1+$A$39)^5+$C$29)/$C$32</f>
@@ -3778,7 +3778,7 @@
     </row>
     <row r="40">
       <c r="A40" s="21" t="n">
-        <v>0.1157</v>
+        <v>0.1133</v>
       </c>
       <c r="C40" s="22">
         <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*11/(1+$A$40)^5+$C$29)/$C$32</f>
@@ -3803,7 +3803,7 @@
     </row>
     <row r="41">
       <c r="A41" s="21" t="n">
-        <v>0.1257</v>
+        <v>0.1233</v>
       </c>
       <c r="C41" s="22">
         <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*11/(1+$A$41)^5+$C$29)/$C$32</f>
@@ -3828,7 +3828,7 @@
     </row>
     <row r="42">
       <c r="A42" s="21" t="n">
-        <v>0.1357</v>
+        <v>0.1333</v>
       </c>
       <c r="C42" s="22">
         <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*11/(1+$A$42)^5+$C$29)/$C$32</f>
@@ -3853,7 +3853,7 @@
     </row>
     <row r="43">
       <c r="A43" s="21" t="n">
-        <v>0.1457</v>
+        <v>0.1433</v>
       </c>
       <c r="C43" s="22">
         <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*11/(1+$A$43)^5+$C$29)/$C$32</f>
@@ -3878,7 +3878,7 @@
     </row>
     <row r="44">
       <c r="A44" s="21" t="n">
-        <v>0.1557</v>
+        <v>0.1533</v>
       </c>
       <c r="C44" s="22">
         <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*11/(1+$A$44)^5+$C$29)/$C$32</f>
@@ -3903,7 +3903,7 @@
     </row>
     <row r="45">
       <c r="A45" s="21" t="n">
-        <v>0.1657</v>
+        <v>0.1633</v>
       </c>
       <c r="C45" s="22">
         <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*11/(1+$A$45)^5+$C$29)/$C$32</f>
